--- a/input/attachments/ig-assets/IPS_FHIR_to_CDISC_SDTM/04_StructureDefinition-MedicationRequest-uv-ips_to_SDTM.xlsx
+++ b/input/attachments/ig-assets/IPS_FHIR_to_CDISC_SDTM/04_StructureDefinition-MedicationRequest-uv-ips_to_SDTM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29406"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdisc-my.sharepoint.com/personal/rbaker_cdisc_org/Documents/1 Real World Data - RWD/1_XSHARE/Spreadsheets for project/IPS FHIR 1.1.0 to SDTMIG 3.4_2024-Nov/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="310" documentId="8_{0F867321-5F96-40E0-9856-3942AEC4AC2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64F879B6-E2F1-4B44-839D-21DBC8E2189D}"/>
+  <xr:revisionPtr revIDLastSave="311" documentId="8_{0F867321-5F96-40E0-9856-3942AEC4AC2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E15E1A45-D569-4470-83E0-B2994BBE04F2}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="2415" windowWidth="19635" windowHeight="9960" firstSheet="4" activeTab="4" xr2:uid="{AA3C65A3-3164-4592-AEE2-E540677012EE}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="2415" windowWidth="19635" windowHeight="9960" firstSheet="4" activeTab="6" xr2:uid="{AA3C65A3-3164-4592-AEE2-E540677012EE}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="7" r:id="rId1"/>
@@ -3536,8 +3536,7 @@
     <t xml:space="preserve">CDISC SDTM Study Identifier/STUDYID </t>
   </si>
   <si>
-    <t xml:space="preserve">For each clinical research study, populate the STUDYID variable with a default value "RWDTOSDTM-YYYYMMDD" where the date is the date on which the FHIR dataset was converted to create SDTM datasets.
-</t>
+    <t>In case there is no FHIR study ID (ResearchStudy or ResearchDefinition) available for the patient for which the immunization data is mapped, populate the STUDYID variable with a default value "RWDTOSDTM-YYYYMMDD" where the date is the date on which the FHIR dataset was converted to create SDTM datasets.</t>
   </si>
   <si>
     <t xml:space="preserve">Study Identifier/STUDYID is a variable in CDISC Demographics domain that is a unique identifier for a study. STUDYID is used as a key in all CDISC SDTM datasets.
@@ -3872,7 +3871,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -3981,6 +3980,13 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="11">
@@ -4175,7 +4181,7 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -4323,35 +4329,20 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -18492,7 +18483,7 @@
         <v>688</v>
       </c>
       <c r="AQ19" s="50"/>
-      <c r="AR19" s="62" t="s">
+      <c r="AR19" s="61" t="s">
         <v>689</v>
       </c>
     </row>
@@ -20220,7 +20211,7 @@
       <c r="AO34" s="57" t="s">
         <v>679</v>
       </c>
-      <c r="AP34" s="63" t="s">
+      <c r="AP34" s="7" t="s">
         <v>696</v>
       </c>
       <c r="AQ34" s="50"/>
@@ -21830,7 +21821,7 @@
         <v>698</v>
       </c>
       <c r="AQ48" s="50"/>
-      <c r="AR48" s="62" t="s">
+      <c r="AR48" s="61" t="s">
         <v>699</v>
       </c>
     </row>
@@ -22180,11 +22171,11 @@
       <c r="AO51" s="57" t="s">
         <v>679</v>
       </c>
-      <c r="AP51" s="64" t="s">
+      <c r="AP51" s="62" t="s">
         <v>700</v>
       </c>
       <c r="AQ51" s="50"/>
-      <c r="AR51" s="62" t="s">
+      <c r="AR51" s="61" t="s">
         <v>701</v>
       </c>
     </row>
@@ -27146,11 +27137,11 @@
       <c r="AO97" s="7" t="s">
         <v>679</v>
       </c>
-      <c r="AP97" s="63" t="s">
+      <c r="AP97" s="7" t="s">
         <v>706</v>
       </c>
       <c r="AQ97" s="50"/>
-      <c r="AR97" s="65" t="s">
+      <c r="AR97" s="61" t="s">
         <v>707</v>
       </c>
     </row>
@@ -27172,11 +27163,11 @@
       <c r="AO98" s="7" t="s">
         <v>679</v>
       </c>
-      <c r="AP98" s="63" t="s">
+      <c r="AP98" s="7" t="s">
         <v>709</v>
       </c>
       <c r="AQ98" s="50"/>
-      <c r="AR98" s="65" t="s">
+      <c r="AR98" s="61" t="s">
         <v>710</v>
       </c>
     </row>
@@ -27228,7 +27219,7 @@
         <v>714</v>
       </c>
       <c r="AQ100" s="50"/>
-      <c r="AR100" s="62" t="s">
+      <c r="AR100" s="61" t="s">
         <v>715</v>
       </c>
     </row>
@@ -27347,7 +27338,7 @@
       <c r="B2" s="20">
         <v>1</v>
       </c>
-      <c r="C2" s="65" t="s">
+      <c r="C2" s="61" t="s">
         <v>727</v>
       </c>
       <c r="D2" s="20" t="s">
@@ -27383,7 +27374,7 @@
       <c r="B3" s="20">
         <v>2</v>
       </c>
-      <c r="C3" s="65" t="s">
+      <c r="C3" s="61" t="s">
         <v>727</v>
       </c>
       <c r="D3" s="20" t="s">
@@ -27395,7 +27386,7 @@
       <c r="F3" s="7" t="s">
         <v>679</v>
       </c>
-      <c r="G3" s="63" t="s">
+      <c r="G3" s="7" t="s">
         <v>684</v>
       </c>
       <c r="H3" s="6" t="s">
@@ -27419,7 +27410,7 @@
       <c r="B4" s="20">
         <v>3</v>
       </c>
-      <c r="C4" s="65" t="s">
+      <c r="C4" s="61" t="s">
         <v>727</v>
       </c>
       <c r="D4" s="20" t="s">
@@ -27455,7 +27446,7 @@
       <c r="B5" s="20">
         <v>4</v>
       </c>
-      <c r="C5" s="65" t="s">
+      <c r="C5" s="61" t="s">
         <v>727</v>
       </c>
       <c r="D5" s="20" t="s">
@@ -27491,7 +27482,7 @@
       <c r="B6" s="20">
         <v>5</v>
       </c>
-      <c r="C6" s="65" t="s">
+      <c r="C6" s="61" t="s">
         <v>727</v>
       </c>
       <c r="D6" s="20" t="s">
@@ -27503,10 +27494,10 @@
       <c r="F6" s="7" t="s">
         <v>679</v>
       </c>
-      <c r="G6" s="63" t="s">
+      <c r="G6" s="7" t="s">
         <v>688</v>
       </c>
-      <c r="H6" s="62" t="s">
+      <c r="H6" s="61" t="s">
         <v>738</v>
       </c>
       <c r="I6" s="19"/>
@@ -27527,7 +27518,7 @@
       <c r="B7" s="20">
         <v>5</v>
       </c>
-      <c r="C7" s="65" t="s">
+      <c r="C7" s="61" t="s">
         <v>727</v>
       </c>
       <c r="D7" s="20" t="s">
@@ -27563,10 +27554,10 @@
       <c r="B8" s="20">
         <v>6</v>
       </c>
-      <c r="C8" s="65" t="s">
+      <c r="C8" s="61" t="s">
         <v>727</v>
       </c>
-      <c r="D8" s="66" t="s">
+      <c r="D8" s="63" t="s">
         <v>740</v>
       </c>
       <c r="E8" s="20" t="s">
@@ -27599,10 +27590,10 @@
       <c r="B9" s="20">
         <v>7</v>
       </c>
-      <c r="C9" s="65" t="s">
+      <c r="C9" s="61" t="s">
         <v>727</v>
       </c>
-      <c r="D9" s="65" t="s">
+      <c r="D9" s="61" t="s">
         <v>742</v>
       </c>
       <c r="E9" s="20" t="s">
@@ -27635,19 +27626,19 @@
       <c r="B10" s="20">
         <v>8</v>
       </c>
-      <c r="C10" s="65" t="s">
+      <c r="C10" s="61" t="s">
         <v>727</v>
       </c>
       <c r="D10" s="20" t="s">
         <v>744</v>
       </c>
-      <c r="E10" s="67" t="s">
+      <c r="E10" s="20" t="s">
         <v>745</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>679</v>
       </c>
-      <c r="G10" s="63" t="s">
+      <c r="G10" s="7" t="s">
         <v>696</v>
       </c>
       <c r="H10" s="5" t="s">
@@ -27671,7 +27662,7 @@
       <c r="B11" s="20">
         <v>9</v>
       </c>
-      <c r="C11" s="65" t="s">
+      <c r="C11" s="61" t="s">
         <v>727</v>
       </c>
       <c r="D11" s="20" t="s">
@@ -27686,7 +27677,7 @@
       <c r="G11" s="7" t="s">
         <v>698</v>
       </c>
-      <c r="H11" s="62" t="s">
+      <c r="H11" s="61" t="s">
         <v>699</v>
       </c>
       <c r="I11" s="19"/>
@@ -27707,7 +27698,7 @@
       <c r="B12" s="20">
         <v>10</v>
       </c>
-      <c r="C12" s="65" t="s">
+      <c r="C12" s="61" t="s">
         <v>727</v>
       </c>
       <c r="D12" s="20" t="s">
@@ -27719,10 +27710,10 @@
       <c r="F12" s="7" t="s">
         <v>679</v>
       </c>
-      <c r="G12" s="64" t="s">
+      <c r="G12" s="62" t="s">
         <v>700</v>
       </c>
-      <c r="H12" s="62" t="s">
+      <c r="H12" s="61" t="s">
         <v>701</v>
       </c>
       <c r="I12" s="19"/>
@@ -27743,7 +27734,7 @@
       <c r="B13" s="20">
         <v>11</v>
       </c>
-      <c r="C13" s="65" t="s">
+      <c r="C13" s="61" t="s">
         <v>727</v>
       </c>
       <c r="D13" s="20" t="s">
@@ -27779,7 +27770,7 @@
       <c r="B14" s="20">
         <v>12</v>
       </c>
-      <c r="C14" s="65" t="s">
+      <c r="C14" s="61" t="s">
         <v>727</v>
       </c>
       <c r="D14" s="20" t="s">
@@ -27791,10 +27782,10 @@
       <c r="F14" s="7" t="s">
         <v>679</v>
       </c>
-      <c r="G14" s="63" t="s">
+      <c r="G14" s="7" t="s">
         <v>706</v>
       </c>
-      <c r="H14" s="65" t="s">
+      <c r="H14" s="61" t="s">
         <v>707</v>
       </c>
       <c r="I14" s="19"/>
@@ -27815,7 +27806,7 @@
       <c r="B15" s="20">
         <v>13</v>
       </c>
-      <c r="C15" s="65" t="s">
+      <c r="C15" s="61" t="s">
         <v>727</v>
       </c>
       <c r="D15" s="20" t="s">
@@ -27827,10 +27818,10 @@
       <c r="F15" s="7" t="s">
         <v>679</v>
       </c>
-      <c r="G15" s="63" t="s">
+      <c r="G15" s="7" t="s">
         <v>709</v>
       </c>
-      <c r="H15" s="65" t="s">
+      <c r="H15" s="61" t="s">
         <v>710</v>
       </c>
       <c r="I15" s="19"/>
@@ -27851,7 +27842,7 @@
       <c r="B16" s="20">
         <v>14</v>
       </c>
-      <c r="C16" s="65" t="s">
+      <c r="C16" s="61" t="s">
         <v>727</v>
       </c>
       <c r="D16" s="20" t="s">
@@ -27887,7 +27878,7 @@
       <c r="B17" s="20">
         <v>9</v>
       </c>
-      <c r="C17" s="65" t="s">
+      <c r="C17" s="61" t="s">
         <v>727</v>
       </c>
       <c r="D17" s="20" t="s">
@@ -27902,7 +27893,7 @@
       <c r="G17" s="7" t="s">
         <v>714</v>
       </c>
-      <c r="H17" s="62" t="s">
+      <c r="H17" s="61" t="s">
         <v>715</v>
       </c>
       <c r="I17" s="19"/>
@@ -27923,7 +27914,7 @@
       <c r="B18" s="20">
         <v>9</v>
       </c>
-      <c r="C18" s="65" t="s">
+      <c r="C18" s="61" t="s">
         <v>727</v>
       </c>
       <c r="D18" s="20" t="s">
@@ -27959,7 +27950,7 @@
       <c r="B19" s="20">
         <v>15</v>
       </c>
-      <c r="C19" s="65" t="s">
+      <c r="C19" s="61" t="s">
         <v>727</v>
       </c>
       <c r="D19" s="20" t="s">
@@ -27995,7 +27986,7 @@
       <c r="B20" s="20">
         <v>16</v>
       </c>
-      <c r="C20" s="65" t="s">
+      <c r="C20" s="61" t="s">
         <v>727</v>
       </c>
       <c r="D20" s="20" t="s">
@@ -28031,7 +28022,7 @@
       <c r="B21" s="20">
         <v>17</v>
       </c>
-      <c r="C21" s="65" t="s">
+      <c r="C21" s="61" t="s">
         <v>727</v>
       </c>
       <c r="D21" s="20" t="s">
@@ -28064,37 +28055,37 @@
       <c r="A22" s="20">
         <v>21</v>
       </c>
-      <c r="B22" s="68">
+      <c r="B22" s="10">
         <v>10</v>
       </c>
-      <c r="C22" s="65" t="s">
+      <c r="C22" s="61" t="s">
         <v>727</v>
       </c>
-      <c r="D22" s="67" t="s">
+      <c r="D22" s="20" t="s">
         <v>761</v>
       </c>
-      <c r="E22" s="67" t="s">
+      <c r="E22" s="20" t="s">
         <v>762</v>
       </c>
-      <c r="F22" s="63" t="s">
+      <c r="F22" s="7" t="s">
         <v>763</v>
       </c>
-      <c r="G22" s="63" t="s">
+      <c r="G22" s="7" t="s">
         <v>764</v>
       </c>
-      <c r="H22" s="69" t="s">
+      <c r="H22" s="8" t="s">
         <v>765</v>
       </c>
-      <c r="I22" s="70"/>
-      <c r="J22" s="70"/>
-      <c r="K22" s="70"/>
-      <c r="L22" s="70"/>
-      <c r="M22" s="70"/>
-      <c r="N22" s="70"/>
-      <c r="O22" s="70"/>
-      <c r="P22" s="70"/>
-      <c r="Q22" s="70"/>
-      <c r="R22" s="70"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
+      <c r="R22" s="19"/>
     </row>
     <row r="25" spans="1:18">
       <c r="G25"/>
@@ -31022,10 +31013,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="64" t="s">
         <v>892</v>
       </c>
-      <c r="B1" s="61"/>
+      <c r="B1" s="64"/>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
     </row>
@@ -31069,14 +31060,14 @@
         <v>900</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="57.6">
+    <row r="5" spans="1:4" ht="57.75">
       <c r="A5" s="7">
         <v>3</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>901</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="65" t="s">
         <v>902</v>
       </c>
       <c r="D5" s="5" t="s">
@@ -31303,17 +31294,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100699A48AB9E19DA4AB64847A071655FFB" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9c43450b8c34e20acaf1756fc6612395">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a46baf18-fe18-4a25-9dd7-6596c31699af" xmlns:ns3="526f0e77-c4a1-4bb9-a981-799c4b6cfc2b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a2045bb9c165ab785731dcc392b30c8" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100699A48AB9E19DA4AB64847A071655FFB" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fb735b3d8e016bb6466dda22f76823b1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a46baf18-fe18-4a25-9dd7-6596c31699af" xmlns:ns3="526f0e77-c4a1-4bb9-a981-799c4b6cfc2b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="47d37a05d05a9fe6c5dd27e72eaf287f" ns2:_="" ns3:_="">
     <xsd:import namespace="a46baf18-fe18-4a25-9dd7-6596c31699af"/>
     <xsd:import namespace="526f0e77-c4a1-4bb9-a981-799c4b6cfc2b"/>
     <xsd:element name="properties">
@@ -31336,6 +31318,7 @@
                 <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -31403,6 +31386,11 @@
     <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="23" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -31546,14 +31534,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75C93858-B6BA-4220-B735-DB356EA2A5D1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAFCE1E3-75D5-4A87-AD07-BC360D99440A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EF1D1B6-63EB-4D2A-8A8F-893E13E92BBA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{273885B1-F4A4-4F3A-A27C-D6916A0EB584}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAFCE1E3-75D5-4A87-AD07-BC360D99440A}"/>
 </file>